--- a/pds_admin_WB/Backend/Backend/Tagging_Sheet_Pre.xlsx
+++ b/pds_admin_WB/Backend/Backend/Tagging_Sheet_Pre.xlsx
@@ -441,7 +441,7 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>
@@ -467,13 +467,13 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F3" t="s">
         <v>8</v>
@@ -493,13 +493,13 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" t="s">
         <v>8</v>
@@ -519,13 +519,13 @@
         <v>7</v>
       </c>
       <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5">
         <v>3</v>
-      </c>
-      <c r="D5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
       </c>
       <c r="F5" t="s">
         <v>8</v>
